--- a/tests/workbooktests/workbooks/test_dividends.xlsx
+++ b/tests/workbooktests/workbooks/test_dividends.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sebastian\01_GitHub\sschlenkrich\QuantLibXlOil\tests\workbooks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sebastian\01_GitHub\sschlenkrich\QuantLibXlOil\tests\workbooktests\workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{059DC1AF-0E99-4C1A-BDDB-2288569E935B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3279E2BB-ECB2-43E1-8677-D94957900262}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11010" yWindow="-19485" windowWidth="27375" windowHeight="18150" xr2:uid="{0C387F45-4188-46D7-BB29-3B0CE3AA2B19}"/>
+    <workbookView xWindow="3450" yWindow="-18675" windowWidth="30690" windowHeight="16530" xr2:uid="{0C387F45-4188-46D7-BB29-3B0CE3AA2B19}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -451,7 +451,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A12A55D0-2898-40E2-B56E-54043A13B337}">
-  <dimension ref="A2:D15"/>
+  <dimension ref="A2:D13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25.33203125" customWidth="1"/>
@@ -495,43 +495,30 @@
       <c r="A7" t="s">
         <v>3</v>
       </c>
-      <c r="B7" t="str" cm="1">
-        <f t="array" ref="B7">_xll.qlFixedDividend(B3,B2)</f>
-        <v>⚡[Book1]Sheet1!R7C2FixedDividend,A</v>
-      </c>
-      <c r="C7" s="1" cm="1">
-        <f t="array" ref="C7">_xll.qlCashFlowDate(B7)</f>
-        <v>46174</v>
-      </c>
-      <c r="D7" cm="1">
-        <f t="array" ref="D7">_xll.qlCashFlowAmount(B7)</f>
-        <v>100</v>
+      <c r="B7" t="e" cm="1">
+        <f t="array" aca="1" ref="B7" ca="1">_xll.qlFixedDividend(B3,B2)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C7" s="1" t="e" cm="1">
+        <f t="array" aca="1" ref="C7" ca="1">_xll.qlCashFlowDate(B7)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D7" t="e" cm="1">
+        <f t="array" aca="1" ref="D7" ca="1">_xll.qlCashFlowAmount(B7)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>4</v>
       </c>
-      <c r="B8" t="str" cm="1">
-        <f t="array" ref="B8">_xll.qlFractionalDividend(B4,B2)</f>
-        <v>⚡[Book1]Sheet1!R8C2FractionalDividend,A</v>
-      </c>
-      <c r="C8" s="1" cm="1">
-        <f t="array" ref="C8">_xll.qlCashFlowDate(B8)</f>
-        <v>46174</v>
-      </c>
-      <c r="D8" t="str" cm="1">
-        <f t="array" ref="D8">_xll.qlCashFlowAmount(B8)</f>
-        <v xml:space="preserve">RuntimeError: RuntimeError: no nominal given
-Traceback (most recent call last):
-  File "C:\Users\Sebastian\01_GitHub\sschlenkrich\QuantLibXlOil\src\quantlib_xloil\cashflows.py", line 152, in qlCashFlowAmount
-    return cashflow.amount()
-           ~~~~~~~~~~~~~~~^^
-  File "C:\Users\Sebastian\.conda\envs\xloil\Lib\site-packages\QuantLib\QuantLib.py", line 13464, in amount
-    return _QuantLib.CashFlow_amount(self)
-           ~~~~~~~~~~~~~~~~~~~~~~~~~^^^^^^
-RuntimeError: no nominal given
-</v>
+      <c r="B8" t="e" cm="1">
+        <f t="array" aca="1" ref="B8" ca="1">_xll.qlFractionalDividend(B4,B2)</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="C8" s="1" t="e" cm="1">
+        <f t="array" aca="1" ref="C8" ca="1">_xll.qlCashFlowDate(B8)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
@@ -564,19 +551,9 @@
       <c r="A13" t="s">
         <v>5</v>
       </c>
-      <c r="B13" t="str" cm="1">
-        <f t="array" ref="B13:B15">_xll.qlDividendVector(B10:B12,C10:C12)</f>
-        <v>⚡[Book1]Sheet1!R13C2Dividend,A</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B14" t="str">
-        <v>⚡[Book1]Sheet1!R13C2Dividend,B</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B15" t="str">
-        <v>⚡[Book1]Sheet1!R13C2Dividend,C</v>
+      <c r="B13" t="e" cm="1">
+        <f t="array" aca="1" ref="B13" ca="1">_xll.qlDividendVector(B10:B12,C10:C12)</f>
+        <v>#VALUE!</v>
       </c>
     </row>
   </sheetData>

--- a/tests/workbooktests/workbooks/test_dividends.xlsx
+++ b/tests/workbooktests/workbooks/test_dividends.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sebastian\01_GitHub\sschlenkrich\QuantLibXlOil\tests\workbooktests\workbooks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3279E2BB-ECB2-43E1-8677-D94957900262}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95F6F1B6-2E2F-48C2-8E46-4FACDF124FDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3450" yWindow="-18675" windowWidth="30690" windowHeight="16530" xr2:uid="{0C387F45-4188-46D7-BB29-3B0CE3AA2B19}"/>
+    <workbookView xWindow="-120" yWindow="-21720" windowWidth="38640" windowHeight="21120" xr2:uid="{0C387F45-4188-46D7-BB29-3B0CE3AA2B19}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -451,7 +451,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A12A55D0-2898-40E2-B56E-54043A13B337}">
-  <dimension ref="A2:D13"/>
+  <dimension ref="A2:D15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25.33203125" customWidth="1"/>
@@ -495,30 +495,30 @@
       <c r="A7" t="s">
         <v>3</v>
       </c>
-      <c r="B7" t="e" cm="1">
-        <f t="array" aca="1" ref="B7" ca="1">_xll.qlFixedDividend(B3,B2)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C7" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="C7" ca="1">_xll.qlCashFlowDate(B7)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D7" t="e" cm="1">
-        <f t="array" aca="1" ref="D7" ca="1">_xll.qlCashFlowAmount(B7)</f>
-        <v>#VALUE!</v>
+      <c r="B7" t="str" cm="1">
+        <f t="array" ref="B7">_xll.qlFixedDividend(B3,B2)</f>
+        <v>欣[test_dividends.xlsx]Sheet1!R7C2FixedDividend,A</v>
+      </c>
+      <c r="C7" s="1" cm="1">
+        <f t="array" ref="C7">_xll.qlCashFlowDate(B7)</f>
+        <v>46174</v>
+      </c>
+      <c r="D7" cm="1">
+        <f t="array" ref="D7">_xll.qlCashFlowAmount(B7)</f>
+        <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>4</v>
       </c>
-      <c r="B8" t="e" cm="1">
-        <f t="array" aca="1" ref="B8" ca="1">_xll.qlFractionalDividend(B4,B2)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="C8" s="1" t="e" cm="1">
-        <f t="array" aca="1" ref="C8" ca="1">_xll.qlCashFlowDate(B8)</f>
-        <v>#VALUE!</v>
+      <c r="B8" t="str" cm="1">
+        <f t="array" ref="B8">_xll.qlFractionalDividend(B4,B2)</f>
+        <v>欣[test_dividends.xlsx]Sheet1!R8C2FractionalDividend,A</v>
+      </c>
+      <c r="C8" s="1" cm="1">
+        <f t="array" ref="C8">_xll.qlCashFlowDate(B8)</f>
+        <v>46174</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
@@ -551,9 +551,19 @@
       <c r="A13" t="s">
         <v>5</v>
       </c>
-      <c r="B13" t="e" cm="1">
-        <f t="array" aca="1" ref="B13" ca="1">_xll.qlDividendVector(B10:B12,C10:C12)</f>
-        <v>#VALUE!</v>
+      <c r="B13" t="str" cm="1">
+        <f t="array" ref="B13:B15">_xll.qlDividendVector(B10:B12,C10:C12)</f>
+        <v>欣[test_dividends.xlsx]Sheet1!R13C2Dividend,A</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B14" t="str">
+        <v>欣[test_dividends.xlsx]Sheet1!R13C2Dividend,B</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B15" t="str">
+        <v>欣[test_dividends.xlsx]Sheet1!R13C2Dividend,C</v>
       </c>
     </row>
   </sheetData>
